--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34F.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34F.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -121,28 +121,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Subdirección  de Planeación y Evaluación</t>
-  </si>
-  <si>
-    <t>15/07/2022</t>
-  </si>
-  <si>
-    <t>AD348A51F1C789D5FA9DA3559A2B1D05</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 1 de abril de 2022 al 30 de junio de 2022 , el Colegio de Bachilleres del Estado de Tlaxcala, no reporta ningun inmueble como baja.</t>
+    <t>FAA15C03B0CEB18E67C4C985537B25F5</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>no aplica</t>
+  </si>
+  <si>
+    <t>06/07/2023</t>
+  </si>
+  <si>
+    <t>subdirección de planeación y evaluación</t>
+  </si>
+  <si>
+    <t>no hubo bajas en este trimestre</t>
   </si>
 </sst>
 </file>
@@ -538,7 +538,7 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -549,7 +549,7 @@
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="132.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
@@ -712,31 +712,31 @@
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>40</v>
